--- a/resources/Programmes/programmeclasseCM1.xlsx
+++ b/resources/Programmes/programmeclasseCM1.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\JANGAA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\colyl\Documents\Alymia\Gestion scolaire\Back\Gestion-Scolaire\resources\Programmes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39440F37-2C50-48BB-B42F-805E992B949E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11280"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="135">
   <si>
     <t>Matière</t>
   </si>
@@ -446,12 +445,15 @@
   <si>
     <t>Évaluation de la compréhension écrite
 Présentations orales</t>
+  </si>
+  <si>
+    <t>NULL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -729,12 +731,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -783,7 +785,7 @@
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -812,7 +814,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
@@ -838,7 +840,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -864,7 +866,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>29</v>
       </c>
@@ -890,7 +892,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>34</v>
       </c>
@@ -916,7 +918,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>39</v>
       </c>
@@ -945,7 +947,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>47</v>
       </c>
@@ -971,10 +973,13 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>52</v>
       </c>
+      <c r="B11" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="C11" s="4" t="s">
         <v>53</v>
       </c>
@@ -997,7 +1002,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>58</v>
       </c>
@@ -1024,7 +1029,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
         <v>64</v>
       </c>
@@ -1042,7 +1047,7 @@
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="69" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>68</v>
       </c>
@@ -1071,7 +1076,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>76</v>
       </c>
@@ -1097,7 +1102,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>81</v>
       </c>
@@ -1123,7 +1128,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
         <v>87</v>
       </c>
@@ -1149,10 +1154,13 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>93</v>
       </c>
+      <c r="B21" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="C21" s="4" t="s">
         <v>94</v>
       </c>
@@ -1175,10 +1183,13 @@
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="124.2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>100</v>
       </c>
+      <c r="B23" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="C23" s="4" t="s">
         <v>101</v>
       </c>
@@ -1201,10 +1212,13 @@
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="165.6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>105</v>
       </c>
+      <c r="B25" t="s">
+        <v>134</v>
+      </c>
       <c r="C25" s="4" t="s">
         <v>106</v>
       </c>
@@ -1227,7 +1241,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>110</v>
       </c>
@@ -1256,7 +1270,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="57" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B28" s="4" t="s">
         <v>115</v>
       </c>
@@ -1274,7 +1288,7 @@
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
     </row>
-    <row r="30" spans="1:9" ht="57" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>119</v>
       </c>
@@ -1303,7 +1317,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="57" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
         <v>125</v>
       </c>
@@ -1321,9 +1335,12 @@
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
     </row>
-    <row r="33" spans="1:9" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="124.2" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>129</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>134</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>130</v>

--- a/resources/Programmes/programmeclasseCM1.xlsx
+++ b/resources/Programmes/programmeclasseCM1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\colyl\Documents\Alymia\Gestion scolaire\Back\Gestion-Scolaire\resources\Programmes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\gestionscolaire\resources\Programmes\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11280"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7155"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="136">
   <si>
     <t>Matière</t>
   </si>
@@ -175,9 +175,6 @@
   </si>
   <si>
     <t>Fiche d'observation, test écrit</t>
-  </si>
-  <si>
-    <t>EPS</t>
   </si>
   <si>
     <t>1. Apprendre des règles de sécurité
@@ -448,6 +445,12 @@
   </si>
   <si>
     <t>NULL</t>
+  </si>
+  <si>
+    <t>heure_debut</t>
+  </si>
+  <si>
+    <t>heure_fin</t>
   </si>
 </sst>
 </file>
@@ -735,10 +738,19 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA33"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AC23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
+    <col min="8" max="10" width="17.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -764,10 +776,14 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
@@ -784,8 +800,10 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
-    </row>
-    <row r="2" spans="1:27" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
+    </row>
+    <row r="2" spans="1:29" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -811,10 +829,19 @@
         <v>16</v>
       </c>
       <c r="I2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>133</v>
+      </c>
       <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
@@ -837,10 +864,19 @@
         <v>23</v>
       </c>
       <c r="I3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>133</v>
+      </c>
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -863,10 +899,19 @@
         <v>28</v>
       </c>
       <c r="I4" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K4" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>133</v>
+      </c>
       <c r="B5" s="4" t="s">
         <v>29</v>
       </c>
@@ -889,10 +934,19 @@
         <v>33</v>
       </c>
       <c r="I5" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>133</v>
+      </c>
       <c r="B6" s="4" t="s">
         <v>34</v>
       </c>
@@ -915,24 +969,65 @@
         <v>38</v>
       </c>
       <c r="I6" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="7" spans="1:29" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
         <v>39</v>
       </c>
+      <c r="B7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>133</v>
+      </c>
       <c r="B8" s="4" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>44</v>
@@ -941,427 +1036,536 @@
         <v>44</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="I8" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K8" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>133</v>
+      </c>
       <c r="B9" s="4" t="s">
-        <v>47</v>
+        <v>133</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="4">
+        <v>2</v>
+      </c>
+      <c r="G10" s="4">
         <v>50</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="H10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="57" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="96.6" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="G14" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4" t="s">
+      <c r="G16" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" s="4">
+        <v>2</v>
+      </c>
+      <c r="G19" s="4">
+        <v>50</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="4">
+      <c r="I19" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B20" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F21" s="4">
         <v>2</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G21" s="4">
         <v>50</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H21" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K21" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-    </row>
-    <row r="16" spans="1:27" ht="69" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="82.8" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="110.4" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="124.2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="165.6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B25" t="s">
-        <v>134</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="F27" s="4">
-        <v>2</v>
-      </c>
-      <c r="G27" s="4">
-        <v>50</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="B28" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-    </row>
-    <row r="30" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F30" s="4">
-        <v>2</v>
-      </c>
-      <c r="G30" s="4">
-        <v>50</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="B31" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-    </row>
-    <row r="33" spans="1:9" ht="124.2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>99</v>
+        <v>133</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
